--- a/DPC Sprayer Calculator/chemical_library.xlsx
+++ b/DPC Sprayer Calculator/chemical_library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://deadplantclub-my.sharepoint.com/personal/john_terhesh_deadplantclub_com/Documents/DPC Sprayer Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF0E90C0-05D9-4762-8344-FFA3F48E89E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="8_{FF0E90C0-05D9-4762-8344-FFA3F48E89E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ACC5A60-87D6-48F0-8ED3-862B1AF6D719}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="169">
   <si>
     <t>Product</t>
   </si>
@@ -489,13 +489,52 @@
   </si>
   <si>
     <t>fl oz/100gal</t>
+  </si>
+  <si>
+    <t>Roundup Concentrate 41%</t>
+  </si>
+  <si>
+    <t>Glyphosate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Emergence </t>
+  </si>
+  <si>
+    <t>https://www.cdms.net/ldat/mp8JK008.pdf</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>Cheetah Pro 24.5%</t>
+  </si>
+  <si>
+    <t>Glufosinate-ammonium</t>
+  </si>
+  <si>
+    <t>https://www.aacounty.org/sites/default/files/2024-05/Cheetah-Pro-Label.pdf</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>Rezilon</t>
+  </si>
+  <si>
+    <t>Alion</t>
+  </si>
+  <si>
+    <t>https://assets.greenbook.net/16-31-06-08-02-2022-Rezilon_-_label.pdf</t>
+  </si>
+  <si>
+    <t>https://cs-assets.bayer.com/is/content/bayer/Alion_Herbicide_Label1qpdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -509,6 +548,10 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -537,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -557,11 +600,78 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF990000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF990000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -747,27 +857,23 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ChemicalLibraryTable" displayName="ChemicalLibraryTable" ref="A1:N34" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ChemicalLibraryTable" displayName="ChemicalLibraryTable" ref="A1:N38" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Product" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Category" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Active Ingredient" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Application / Use" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Rate Basis" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Water Required (gal/acre)" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Proposed Label Low" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Proposed Label High" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Label Units" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Calibration Required?" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Source / Label URL" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Date Added" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Label Verified?" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Verification Date" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Product" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Category" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Active Ingredient" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Application / Use" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Rate Basis" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Water Required (gal/acre)" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Proposed Label Low" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Proposed Label High" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Label Units" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Calibration Required?" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Source / Label URL" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Date Added" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Label Verified?" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Verification Date" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -968,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -980,7 +1086,7 @@
     <col min="7" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="11" max="11" width="63.125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="14" width="16" customWidth="1"/>
   </cols>
@@ -1181,10 +1287,10 @@
         <v>40</v>
       </c>
       <c r="G5" s="3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H5" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>24</v>
@@ -2443,8 +2549,211 @@
         <v>46285</v>
       </c>
     </row>
+    <row r="35" spans="1:14" ht="21" customHeight="1">
+      <c r="A35" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7">
+        <v>150</v>
+      </c>
+      <c r="H35" s="7">
+        <v>300</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="N35" s="5">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="21" customHeight="1">
+      <c r="A36" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="3">
+        <v>40</v>
+      </c>
+      <c r="G36" s="3">
+        <v>3</v>
+      </c>
+      <c r="H36" s="3">
+        <v>5</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N36" s="5">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="21" customHeight="1">
+      <c r="A37" t="s">
+        <v>166</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="3">
+        <v>40</v>
+      </c>
+      <c r="G37" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="H37" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N37" s="5">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="24" customHeight="1">
+      <c r="A38" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" t="s">
+        <v>162</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7">
+        <v>50</v>
+      </c>
+      <c r="H38" s="7">
+        <v>200</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="N38" s="5">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="5"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:M34">
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="M2:M40">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>M2="Needs Review"</formula>
     </cfRule>
@@ -2456,13 +2765,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="B2:B34" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="B2:B40" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Herbicide,Insecticide,Fungicide,Miticide/Insecticide"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J2:J34" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="J2:J40" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M2:M34" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" sqref="M2:M40" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Needs Review,Verified,Do Not Use"</formula1>
     </dataValidation>
   </dataValidations>
